--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -709,10 +709,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3275400</v>
+        <v>3266400</v>
       </c>
       <c r="E8" s="3">
-        <v>3015900</v>
+        <v>3007700</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -736,10 +736,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1939400</v>
+        <v>1934100</v>
       </c>
       <c r="E9" s="3">
-        <v>1457300</v>
+        <v>1453300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -763,10 +763,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1336000</v>
+        <v>1332300</v>
       </c>
       <c r="E10" s="3">
-        <v>1558700</v>
+        <v>1554400</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -921,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2351500</v>
+        <v>2345100</v>
       </c>
       <c r="E17" s="3">
-        <v>1478900</v>
+        <v>1474900</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -948,10 +948,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>923900</v>
+        <v>921300</v>
       </c>
       <c r="E18" s="3">
-        <v>1537000</v>
+        <v>1532800</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -988,10 +988,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>599800</v>
+        <v>598200</v>
       </c>
       <c r="E20" s="3">
-        <v>511200</v>
+        <v>509800</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1015,7 +1015,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1592800</v>
+        <v>1588500</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
@@ -1042,10 +1042,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>141800</v>
+        <v>141400</v>
       </c>
       <c r="E22" s="3">
-        <v>76900</v>
+        <v>76700</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1069,10 +1069,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1381900</v>
+        <v>1378100</v>
       </c>
       <c r="E23" s="3">
-        <v>1971300</v>
+        <v>1965900</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1096,10 +1096,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>163700</v>
+        <v>163300</v>
       </c>
       <c r="E24" s="3">
-        <v>258700</v>
+        <v>258000</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1150,10 +1150,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1218200</v>
+        <v>1214900</v>
       </c>
       <c r="E26" s="3">
-        <v>1712600</v>
+        <v>1707900</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1177,10 +1177,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1184300</v>
+        <v>1181100</v>
       </c>
       <c r="E27" s="3">
-        <v>1691500</v>
+        <v>1686800</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1312,10 +1312,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-599800</v>
+        <v>-598200</v>
       </c>
       <c r="E32" s="3">
-        <v>-511200</v>
+        <v>-509800</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1339,10 +1339,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1184300</v>
+        <v>1181100</v>
       </c>
       <c r="E33" s="3">
-        <v>1691500</v>
+        <v>1686800</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1393,10 +1393,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1184300</v>
+        <v>1181100</v>
       </c>
       <c r="E35" s="3">
-        <v>1691500</v>
+        <v>1686800</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1478,7 +1478,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1722700</v>
+        <v>1718000</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>3</v>
@@ -1532,7 +1532,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1752100</v>
+        <v>1747300</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -1559,7 +1559,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12467500</v>
+        <v>12433500</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -1586,7 +1586,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>51400</v>
+        <v>51300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -1613,7 +1613,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15993800</v>
+        <v>15950100</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>3</v>
@@ -1640,7 +1640,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17592300</v>
+        <v>17544300</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -1667,7 +1667,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34031800</v>
+        <v>33938800</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -1694,7 +1694,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46700</v>
+        <v>46500</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>3</v>
@@ -1775,7 +1775,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>249300</v>
+        <v>248600</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -1829,7 +1829,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>67913800</v>
+        <v>67728400</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -1882,7 +1882,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1100600</v>
+        <v>1097600</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
@@ -1909,7 +1909,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4272800</v>
+        <v>4261200</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
@@ -1936,7 +1936,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2378700</v>
+        <v>2372200</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -1963,7 +1963,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7752200</v>
+        <v>7731000</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>3</v>
@@ -1990,7 +1990,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14596400</v>
+        <v>14556500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1320200</v>
+        <v>1316600</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
@@ -2125,7 +2125,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>25874100</v>
+        <v>25803500</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>3</v>
@@ -2273,7 +2273,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35502900</v>
+        <v>35405900</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>3</v>
@@ -2381,7 +2381,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>42039700</v>
+        <v>41924900</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1184300</v>
+        <v>1181100</v>
       </c>
       <c r="E81" s="3">
-        <v>1691500</v>
+        <v>1686800</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2507,7 +2507,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>69200</v>
+        <v>69000</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -2669,7 +2669,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1426900</v>
+        <v>1423000</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>3</v>
@@ -2709,7 +2709,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-408400</v>
+        <v>-407300</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -2790,7 +2790,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1557000</v>
+        <v>1552700</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -2830,7 +2830,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1117200</v>
+        <v>-1114100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2731100</v>
+        <v>-2723600</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -2965,7 +2965,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-53100</v>
+        <v>-52900</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -2992,7 +2992,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>199700</v>
+        <v>199200</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -656,40 +656,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
@@ -702,20 +702,23 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3266400</v>
+        <v>3530300</v>
       </c>
       <c r="E8" s="3">
-        <v>3007700</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>3271800</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3012600</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -729,20 +732,23 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1934100</v>
+        <v>2270600</v>
       </c>
       <c r="E9" s="3">
-        <v>1453300</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+        <v>1937300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1455700</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -756,20 +762,23 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1332300</v>
+        <v>1259800</v>
       </c>
       <c r="E10" s="3">
-        <v>1554400</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>1334500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1557000</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -783,9 +792,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,20 +866,23 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8700</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -877,9 +896,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -904,9 +926,12 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,19 +940,20 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2345100</v>
+        <v>2517800</v>
       </c>
       <c r="E17" s="3">
-        <v>1474900</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
+        <v>2348900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1477300</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -941,20 +967,23 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>921300</v>
+        <v>1012500</v>
       </c>
       <c r="E18" s="3">
-        <v>1532800</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+        <v>922900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1535300</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -968,9 +997,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,19 +1014,20 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>598200</v>
+        <v>561100</v>
       </c>
       <c r="E20" s="3">
-        <v>509800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+        <v>599100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>510700</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1008,20 +1041,23 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1588500</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+        <v>1642600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1591100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2110600</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1035,20 +1071,23 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>141400</v>
+        <v>236300</v>
       </c>
       <c r="E22" s="3">
-        <v>76700</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+        <v>141600</v>
+      </c>
+      <c r="F22" s="3">
+        <v>76800</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1062,20 +1101,23 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1378100</v>
+        <v>1337400</v>
       </c>
       <c r="E23" s="3">
-        <v>1965900</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
+        <v>1380400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1969200</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1089,20 +1131,23 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>163300</v>
+        <v>85300</v>
       </c>
       <c r="E24" s="3">
-        <v>258000</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+        <v>163500</v>
+      </c>
+      <c r="F24" s="3">
+        <v>258400</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1116,9 +1161,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,20 +1191,23 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1214900</v>
+        <v>1252100</v>
       </c>
       <c r="E26" s="3">
-        <v>1707900</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
+        <v>1216900</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1710700</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1170,20 +1221,23 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1181100</v>
+        <v>1185900</v>
       </c>
       <c r="E27" s="3">
-        <v>1686800</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
+        <v>1183100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1689600</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1251,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1281,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,20 +1371,23 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-598200</v>
+        <v>-561100</v>
       </c>
       <c r="E32" s="3">
-        <v>-509800</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+        <v>-599100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-510700</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1332,20 +1401,23 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1181100</v>
+        <v>1185900</v>
       </c>
       <c r="E33" s="3">
-        <v>1686800</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
+        <v>1183100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1689600</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1431,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,20 +1461,23 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1181100</v>
+        <v>1185900</v>
       </c>
       <c r="E35" s="3">
-        <v>1686800</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
+        <v>1183100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1689600</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1413,26 +1491,29 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1445,9 +1526,12 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,16 +1557,17 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1718000</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
+        <v>2923300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1720900</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1498,44 +1584,50 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+        <v>61700</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1747300</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+        <v>1293900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1750200</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1552,17 +1644,20 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12433500</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+        <v>12057700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12453900</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1579,18 +1674,21 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>840300</v>
+      </c>
+      <c r="E45" s="3">
         <v>51300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1606,17 +1704,20 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15950100</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
+        <v>17176900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15976300</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1633,17 +1734,20 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17544300</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+        <v>17434600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>17573100</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1660,17 +1764,20 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>33938800</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+        <v>34589300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>33994600</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1687,17 +1794,20 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46500</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+        <v>46100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46600</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,17 +1884,20 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>248600</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+        <v>226600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>249100</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,17 +1944,20 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>67728400</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
+        <v>69473500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>67839600</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,16 +2005,17 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1097600</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+        <v>1208800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1099400</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -1902,17 +2032,20 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4261200</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+        <v>4006900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4268200</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -1929,17 +2062,20 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2372200</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+        <v>2484400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2376100</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -1956,17 +2092,20 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7731000</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
+        <v>7700200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7743700</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -1983,17 +2122,20 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14556500</v>
+        <v>16377600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>14580400</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2010,17 +2152,20 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1316600</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+        <v>1333800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1318800</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,17 +2272,20 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>25803500</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
+        <v>27659800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25845900</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,17 +2436,20 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35405900</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+        <v>35515400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>35464100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,17 +2556,20 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>41924900</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
+        <v>41813700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>41993700</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,26 +2616,29 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2460,20 +2651,23 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1181100</v>
+        <v>1185900</v>
       </c>
       <c r="E81" s="3">
-        <v>1686800</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
+        <v>1183100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1689600</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2681,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,19 +2698,20 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>69000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3">
+        <v>69100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>64700</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,20 +2875,23 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1423000</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>1851600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1425300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>87700</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,19 +2922,20 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-407300</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+        <v>-584900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-7023500</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,20 +3009,23 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1552700</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>2000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1555300</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-6408100</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,19 +3056,20 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1114100</v>
+        <v>-1116000</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-1116000</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1116000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,20 +3173,23 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2723600</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>-693600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2728100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>6665100</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -2958,20 +3203,23 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-52900</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+        <v>-10600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>7000</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -2985,20 +3233,23 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>199200</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
+        <v>1149400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>199500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>351800</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -712,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3530300</v>
+        <v>3535300</v>
       </c>
       <c r="E8" s="3">
-        <v>3271800</v>
+        <v>3276400</v>
       </c>
       <c r="F8" s="3">
-        <v>3012600</v>
+        <v>3016900</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -742,13 +742,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2270600</v>
+        <v>2273800</v>
       </c>
       <c r="E9" s="3">
-        <v>1937300</v>
+        <v>1940000</v>
       </c>
       <c r="F9" s="3">
-        <v>1455700</v>
+        <v>1457700</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -772,13 +772,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1259800</v>
+        <v>1261500</v>
       </c>
       <c r="E10" s="3">
-        <v>1334500</v>
+        <v>1336400</v>
       </c>
       <c r="F10" s="3">
-        <v>1557000</v>
+        <v>1559100</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -947,13 +947,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2517800</v>
+        <v>2521400</v>
       </c>
       <c r="E17" s="3">
-        <v>2348900</v>
+        <v>2352300</v>
       </c>
       <c r="F17" s="3">
-        <v>1477300</v>
+        <v>1479400</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -977,13 +977,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1012500</v>
+        <v>1013900</v>
       </c>
       <c r="E18" s="3">
-        <v>922900</v>
+        <v>924200</v>
       </c>
       <c r="F18" s="3">
-        <v>1535300</v>
+        <v>1537500</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1021,13 +1021,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>561100</v>
+        <v>561900</v>
       </c>
       <c r="E20" s="3">
-        <v>599100</v>
+        <v>600000</v>
       </c>
       <c r="F20" s="3">
-        <v>510700</v>
+        <v>511400</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1051,13 +1051,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1642600</v>
+        <v>1644900</v>
       </c>
       <c r="E21" s="3">
-        <v>1591100</v>
+        <v>1593300</v>
       </c>
       <c r="F21" s="3">
-        <v>2110600</v>
+        <v>2113600</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1081,13 +1081,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>236300</v>
+        <v>236600</v>
       </c>
       <c r="E22" s="3">
-        <v>141600</v>
+        <v>141800</v>
       </c>
       <c r="F22" s="3">
-        <v>76800</v>
+        <v>76900</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1111,13 +1111,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1337400</v>
+        <v>1339200</v>
       </c>
       <c r="E23" s="3">
-        <v>1380400</v>
+        <v>1382300</v>
       </c>
       <c r="F23" s="3">
-        <v>1969200</v>
+        <v>1971900</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1141,13 +1141,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>85300</v>
+        <v>85400</v>
       </c>
       <c r="E24" s="3">
-        <v>163500</v>
+        <v>163700</v>
       </c>
       <c r="F24" s="3">
-        <v>258400</v>
+        <v>258800</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1201,13 +1201,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1252100</v>
+        <v>1253800</v>
       </c>
       <c r="E26" s="3">
-        <v>1216900</v>
+        <v>1218600</v>
       </c>
       <c r="F26" s="3">
-        <v>1710700</v>
+        <v>1713200</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1231,13 +1231,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1185900</v>
+        <v>1187500</v>
       </c>
       <c r="E27" s="3">
-        <v>1183100</v>
+        <v>1184700</v>
       </c>
       <c r="F27" s="3">
-        <v>1689600</v>
+        <v>1692000</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1381,13 +1381,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-561100</v>
+        <v>-561900</v>
       </c>
       <c r="E32" s="3">
-        <v>-599100</v>
+        <v>-600000</v>
       </c>
       <c r="F32" s="3">
-        <v>-510700</v>
+        <v>-511400</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1411,13 +1411,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1185900</v>
+        <v>1187500</v>
       </c>
       <c r="E33" s="3">
-        <v>1183100</v>
+        <v>1184700</v>
       </c>
       <c r="F33" s="3">
-        <v>1689600</v>
+        <v>1692000</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1185900</v>
+        <v>1187500</v>
       </c>
       <c r="E35" s="3">
-        <v>1183100</v>
+        <v>1184700</v>
       </c>
       <c r="F35" s="3">
-        <v>1689600</v>
+        <v>1692000</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1564,10 +1564,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2923300</v>
+        <v>2927400</v>
       </c>
       <c r="E41" s="3">
-        <v>1720900</v>
+        <v>1723300</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>61700</v>
+        <v>61800</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -1624,10 +1624,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1293900</v>
+        <v>1295800</v>
       </c>
       <c r="E43" s="3">
-        <v>1750200</v>
+        <v>1752600</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1654,10 +1654,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12057700</v>
+        <v>12074600</v>
       </c>
       <c r="E44" s="3">
-        <v>12453900</v>
+        <v>12471400</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1684,10 +1684,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>840300</v>
+        <v>841400</v>
       </c>
       <c r="E45" s="3">
-        <v>51300</v>
+        <v>51400</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1714,10 +1714,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17176900</v>
+        <v>17201000</v>
       </c>
       <c r="E46" s="3">
-        <v>15976300</v>
+        <v>15998700</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1744,10 +1744,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17434600</v>
+        <v>17459200</v>
       </c>
       <c r="E47" s="3">
-        <v>17573100</v>
+        <v>17597800</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1774,10 +1774,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34589300</v>
+        <v>34637900</v>
       </c>
       <c r="E48" s="3">
-        <v>33994600</v>
+        <v>34042400</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1804,10 +1804,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46100</v>
+        <v>46200</v>
       </c>
       <c r="E49" s="3">
-        <v>46600</v>
+        <v>46700</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1894,10 +1894,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>226600</v>
+        <v>227000</v>
       </c>
       <c r="E52" s="3">
-        <v>249100</v>
+        <v>249400</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1954,10 +1954,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>69473500</v>
+        <v>69571200</v>
       </c>
       <c r="E54" s="3">
-        <v>67839600</v>
+        <v>67935000</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2012,10 +2012,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1208800</v>
+        <v>1210500</v>
       </c>
       <c r="E57" s="3">
-        <v>1099400</v>
+        <v>1101000</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2042,10 +2042,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4006900</v>
+        <v>4012600</v>
       </c>
       <c r="E58" s="3">
-        <v>4268200</v>
+        <v>4274200</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2072,10 +2072,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2484400</v>
+        <v>2487900</v>
       </c>
       <c r="E59" s="3">
-        <v>2376100</v>
+        <v>2379400</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2102,10 +2102,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7700200</v>
+        <v>7711000</v>
       </c>
       <c r="E60" s="3">
-        <v>7743700</v>
+        <v>7754600</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2132,10 +2132,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16377600</v>
+        <v>16400600</v>
       </c>
       <c r="E61" s="3">
-        <v>14580400</v>
+        <v>14600900</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2162,10 +2162,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1333800</v>
+        <v>1335600</v>
       </c>
       <c r="E62" s="3">
-        <v>1318800</v>
+        <v>1320600</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2282,10 +2282,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27659800</v>
+        <v>27698700</v>
       </c>
       <c r="E66" s="3">
-        <v>25845900</v>
+        <v>25882200</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2446,10 +2446,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35515400</v>
+        <v>35565400</v>
       </c>
       <c r="E72" s="3">
-        <v>35464100</v>
+        <v>35513900</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2566,10 +2566,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>41813700</v>
+        <v>41872500</v>
       </c>
       <c r="E76" s="3">
-        <v>41993700</v>
+        <v>42052800</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2661,13 +2661,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1185900</v>
+        <v>1187500</v>
       </c>
       <c r="E81" s="3">
-        <v>1183100</v>
+        <v>1184700</v>
       </c>
       <c r="F81" s="3">
-        <v>1689600</v>
+        <v>1692000</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2705,13 +2705,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>69000</v>
+        <v>69100</v>
       </c>
       <c r="E83" s="3">
-        <v>69100</v>
+        <v>69200</v>
       </c>
       <c r="F83" s="3">
-        <v>64700</v>
+        <v>64800</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -2885,13 +2885,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1851600</v>
+        <v>1854200</v>
       </c>
       <c r="E89" s="3">
-        <v>1425300</v>
+        <v>1427300</v>
       </c>
       <c r="F89" s="3">
-        <v>87700</v>
+        <v>87800</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2929,13 +2929,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-584900</v>
+        <v>-585800</v>
       </c>
       <c r="E91" s="3">
-        <v>-408000</v>
+        <v>-408500</v>
       </c>
       <c r="F91" s="3">
-        <v>-7023500</v>
+        <v>-7033400</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -3019,13 +3019,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E94" s="3">
-        <v>1555300</v>
+        <v>1557500</v>
       </c>
       <c r="F94" s="3">
-        <v>-6408100</v>
+        <v>-6417100</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3063,13 +3063,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1116000</v>
+        <v>-1117500</v>
       </c>
       <c r="E96" s="3">
-        <v>-1116000</v>
+        <v>-1117500</v>
       </c>
       <c r="F96" s="3">
-        <v>-1116000</v>
+        <v>-1117500</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-693600</v>
+        <v>-694600</v>
       </c>
       <c r="E100" s="3">
-        <v>-2728100</v>
+        <v>-2731900</v>
       </c>
       <c r="F100" s="3">
-        <v>6665100</v>
+        <v>6674500</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3216,10 +3216,10 @@
         <v>-10600</v>
       </c>
       <c r="E101" s="3">
-        <v>-53000</v>
+        <v>-53100</v>
       </c>
       <c r="F101" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3243,13 +3243,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1149400</v>
+        <v>1151000</v>
       </c>
       <c r="E102" s="3">
-        <v>199500</v>
+        <v>199800</v>
       </c>
       <c r="F102" s="3">
-        <v>351800</v>
+        <v>352200</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -690,17 +690,17 @@
       <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3535300</v>
+        <v>3529300</v>
       </c>
       <c r="E8" s="3">
-        <v>3276400</v>
+        <v>3276900</v>
       </c>
       <c r="F8" s="3">
-        <v>3016900</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>3017200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3227000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3104800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2806900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3578400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2273800</v>
+        <v>2269900</v>
       </c>
       <c r="E9" s="3">
-        <v>1940000</v>
+        <v>1940300</v>
       </c>
       <c r="F9" s="3">
-        <v>1457700</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>1457900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1253800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1463200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1286800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1960600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1261500</v>
+        <v>1259400</v>
       </c>
       <c r="E10" s="3">
-        <v>1336400</v>
+        <v>1336600</v>
       </c>
       <c r="F10" s="3">
-        <v>1559100</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>1559300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1973200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1641700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1520200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1617900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="3">
-        <v>-8700</v>
+        <v>18100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-292900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>294800</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-401500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1538700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-1937800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2521400</v>
+        <v>2712300</v>
       </c>
       <c r="E17" s="3">
-        <v>2352300</v>
+        <v>2382200</v>
       </c>
       <c r="F17" s="3">
-        <v>1479400</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>1809000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1595300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1857000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1565500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2380100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1013900</v>
+        <v>817000</v>
       </c>
       <c r="E18" s="3">
-        <v>924200</v>
+        <v>894700</v>
       </c>
       <c r="F18" s="3">
-        <v>1537500</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>1208200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1631700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1247900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1241400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1198300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>561900</v>
+        <v>-685900</v>
       </c>
       <c r="E20" s="3">
-        <v>600000</v>
+        <v>-582400</v>
       </c>
       <c r="F20" s="3">
-        <v>511400</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-487300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-382900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-726400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1552400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1184100</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1644900</v>
+        <v>1528800</v>
       </c>
       <c r="E21" s="3">
-        <v>1593300</v>
+        <v>1501300</v>
       </c>
       <c r="F21" s="3">
-        <v>2113600</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>1714600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2024600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1982600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2802500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2394500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1081,25 +1081,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>236600</v>
+        <v>246800</v>
       </c>
       <c r="E22" s="3">
-        <v>141800</v>
+        <v>102600</v>
       </c>
       <c r="F22" s="3">
-        <v>76900</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>30300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>125600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>139700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>128900</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1339200</v>
+        <v>1336900</v>
       </c>
       <c r="E23" s="3">
-        <v>1382300</v>
+        <v>1382500</v>
       </c>
       <c r="F23" s="3">
-        <v>1971900</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>1972100</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1639800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2450300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4277100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4272400</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>85400</v>
+        <v>85300</v>
       </c>
       <c r="E24" s="3">
-        <v>163700</v>
+        <v>163800</v>
       </c>
       <c r="F24" s="3">
         <v>258800</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>313500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>261500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>271100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>283700</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1253800</v>
+        <v>1251700</v>
       </c>
       <c r="E26" s="3">
-        <v>1218600</v>
+        <v>1218800</v>
       </c>
       <c r="F26" s="3">
-        <v>1713200</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>1713300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1326300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2188800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4006000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3988600</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1187500</v>
+        <v>1185500</v>
       </c>
       <c r="E27" s="3">
-        <v>1184700</v>
+        <v>1184900</v>
       </c>
       <c r="F27" s="3">
-        <v>1692000</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>1692200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2181800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3978500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3943100</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-561900</v>
+        <v>685900</v>
       </c>
       <c r="E32" s="3">
-        <v>-600000</v>
+        <v>582400</v>
       </c>
       <c r="F32" s="3">
-        <v>-511400</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>487300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>382900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>726400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1552400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1184100</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1187500</v>
+        <v>1185500</v>
       </c>
       <c r="E33" s="3">
-        <v>1184700</v>
+        <v>1184900</v>
       </c>
       <c r="F33" s="3">
-        <v>1692000</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>1692200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2181800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3978500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3943100</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1187500</v>
+        <v>1185500</v>
       </c>
       <c r="E35" s="3">
-        <v>1184700</v>
+        <v>1184900</v>
       </c>
       <c r="F35" s="3">
-        <v>1692000</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>1692200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2181800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>3978500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3943100</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1514,17 +1514,17 @@
       <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2927400</v>
+        <v>2768000</v>
       </c>
       <c r="E41" s="3">
-        <v>1723300</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>1448600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1403900</v>
+      </c>
+      <c r="G41" s="3">
+        <v>749000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1378100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2107800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3157800</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1594,25 +1594,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>61800</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>77300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>64500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>49800</v>
+      </c>
+      <c r="G42" s="3">
+        <v>42000</v>
+      </c>
+      <c r="H42" s="3">
+        <v>25200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>30300</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1295800</v>
+        <v>1293500</v>
       </c>
       <c r="E43" s="3">
-        <v>1752600</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>1124600</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1440200</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1522800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1885200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1915600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2222800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12074600</v>
+        <v>12054000</v>
       </c>
       <c r="E44" s="3">
-        <v>12471400</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>12473300</v>
+      </c>
+      <c r="F44" s="3">
+        <v>14001500</v>
+      </c>
+      <c r="G44" s="3">
+        <v>13034300</v>
+      </c>
+      <c r="H44" s="3">
+        <v>12902000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>12408700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>9498900</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>841400</v>
+        <v>346700</v>
       </c>
       <c r="E45" s="3">
         <v>51400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="F45" s="3">
+        <v>126200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>170100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>162400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>395600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>221800</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17201000</v>
+        <v>17171600</v>
       </c>
       <c r="E46" s="3">
-        <v>15998700</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>16001200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>17848400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>16130300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>16529500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>17133600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>15399900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17459200</v>
+        <v>16803700</v>
       </c>
       <c r="E47" s="3">
-        <v>17597800</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>16823100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>17491900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>17562900</v>
+      </c>
+      <c r="H47" s="3">
+        <v>16693900</v>
+      </c>
+      <c r="I47" s="3">
+        <v>14904600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>13822400</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34637900</v>
+        <v>34578600</v>
       </c>
       <c r="E48" s="3">
-        <v>34042400</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>34047600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>34028700</v>
+      </c>
+      <c r="G48" s="3">
+        <v>24214500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>23597400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>22612600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>22249300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46200</v>
+        <v>46100</v>
       </c>
       <c r="E49" s="3">
         <v>46700</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="F49" s="3">
+        <v>47200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>33800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>33600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1894,19 +1894,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>227000</v>
+        <v>95100</v>
       </c>
       <c r="E52" s="3">
-        <v>249400</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>155800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>98600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>170100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>58200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>69571200</v>
+        <v>69452200</v>
       </c>
       <c r="E54" s="3">
-        <v>67935000</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>67945300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>70572300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>59469600</v>
+      </c>
+      <c r="H54" s="3">
+        <v>58446300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>56325800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>52601300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2011,26 +2011,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>1210500</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1101000</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="G57" s="3">
+        <v>531300</v>
+      </c>
+      <c r="H57" s="3">
+        <v>580000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>499000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1111900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4012600</v>
+        <v>4326100</v>
       </c>
       <c r="E58" s="3">
-        <v>4274200</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>4646000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4127500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4029100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4000700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4371500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3199700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2487900</v>
+        <v>2161100</v>
       </c>
       <c r="E59" s="3">
-        <v>2379400</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>1984500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2477400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1946600</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2671800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2862100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2095500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7711000</v>
+        <v>7697800</v>
       </c>
       <c r="E60" s="3">
-        <v>7754600</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>7755800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>8111000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>7059700</v>
+      </c>
+      <c r="H60" s="3">
+        <v>7595900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>7957000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>6407200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16400600</v>
+        <v>16372600</v>
       </c>
       <c r="E61" s="3">
-        <v>14600900</v>
+        <v>14603100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>16027900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>8543200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>8185800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>6893500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>7215100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,22 +2162,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1335600</v>
+        <v>175600</v>
       </c>
       <c r="E62" s="3">
-        <v>1320600</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+        <v>150300</v>
+      </c>
+      <c r="F62" s="3">
+        <v>93000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1700</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27698700</v>
+        <v>25403700</v>
       </c>
       <c r="E66" s="3">
-        <v>25882200</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>23679700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>25408000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>16624500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>16671000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>15720700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>14469300</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>35565400</v>
+        <v>35480300</v>
       </c>
       <c r="E72" s="3">
-        <v>35513900</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>35495100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>35429500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>35024200</v>
+      </c>
+      <c r="H72" s="3">
+        <v>34669400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>33348700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>30241100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>41872500</v>
+        <v>41800900</v>
       </c>
       <c r="E76" s="3">
-        <v>42052800</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>42059200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>42963800</v>
+      </c>
+      <c r="G76" s="3">
+        <v>42253800</v>
+      </c>
+      <c r="H76" s="3">
+        <v>41192300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>39987200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>37444900</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2639,17 +2639,17 @@
       <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1187500</v>
+        <v>1185500</v>
       </c>
       <c r="E81" s="3">
-        <v>1184700</v>
+        <v>1184900</v>
       </c>
       <c r="F81" s="3">
-        <v>1692000</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>1692200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1314500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>2181800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>3978500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>3943100</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>69100</v>
+        <v>68500</v>
       </c>
       <c r="E83" s="3">
-        <v>69200</v>
+        <v>68700</v>
       </c>
       <c r="F83" s="3">
-        <v>64800</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>64400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>55200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>48400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>12000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1854200</v>
+        <v>1851000</v>
       </c>
       <c r="E89" s="3">
-        <v>1427300</v>
+        <v>1427500</v>
       </c>
       <c r="F89" s="3">
         <v>87800</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="G89" s="3">
+        <v>912100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>865800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>488300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-102000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2928,14 +2928,14 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-585800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-408500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-7033400</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E94" s="3">
-        <v>1557500</v>
+        <v>1557700</v>
       </c>
       <c r="F94" s="3">
-        <v>-6417100</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-6417800</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-125600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-490800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-937100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-935200</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,25 +3063,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1117500</v>
+        <v>1115600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1117500</v>
+        <v>1117700</v>
       </c>
       <c r="F96" s="3">
-        <v>-1117500</v>
+        <v>1117600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>1124000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>1045400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>909400</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>771900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-694600</v>
+        <v>-693400</v>
       </c>
       <c r="E100" s="3">
-        <v>-2731900</v>
+        <v>-2732400</v>
       </c>
       <c r="F100" s="3">
-        <v>6674500</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>6675100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-1386600</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-753500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-476500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1930000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3221,17 +3221,17 @@
       <c r="F101" s="3">
         <v>7100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>48500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>134000</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1151000</v>
+        <v>1149000</v>
       </c>
       <c r="E102" s="3">
         <v>199800</v>
       </c>
       <c r="F102" s="3">
-        <v>352200</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>352300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-551600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-419200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-1012500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1026800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3251500</v>
+      </c>
+      <c r="E8" s="3">
         <v>3529300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3276900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3017200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3227000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3104800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2806900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3578400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2105700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2269900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1940300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1457900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1253800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1463200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1286800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1960600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1145800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1259400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1336600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1559300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1973200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1641700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1520200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1617900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-292900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>294800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-401500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1538700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1937800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E15" s="3">
         <v>26000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2153300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2712300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2382200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1809000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1595300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1857000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1565500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2380100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1098200</v>
+      </c>
+      <c r="E18" s="3">
         <v>817000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>894700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1208200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1631700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1247900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1241400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1198300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-373000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-685900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-582400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-487300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-382900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-726400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1552400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1184100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1497300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1528800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1501300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1714600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2024600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1982600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2802500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2394500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>291100</v>
+      </c>
+      <c r="E22" s="3">
         <v>246800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>102600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>125600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>139700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>128900</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1060600</v>
+      </c>
+      <c r="E23" s="3">
         <v>1336900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1382500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1972100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1639800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2450300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4277100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4272400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E24" s="3">
         <v>85300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>163800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>258800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>313500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>261500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>271100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>283700</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>937600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1251700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1218800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1713300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1326300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2188800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4006000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3988600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>810600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1185500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1184900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1692200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1314500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2181800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3978500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3943100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E32" s="3">
         <v>685900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>582400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>487300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>382900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>726400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1552400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1184100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>810600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1185500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1184900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1692200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1314500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2181800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3978500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3943100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>810600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1185500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1184900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1692200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1314500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2181800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3978500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3943100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,278 +1643,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2306900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2768000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1448600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1403900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>749000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1378100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2107800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3157800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E42" s="3">
         <v>77300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>64500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>49800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>42000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1146700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1293500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1124600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1440200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1522800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1885200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1915600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2222800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11021300</v>
+      </c>
+      <c r="E44" s="3">
         <v>12054000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12473300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14001500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13034300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12902000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12408700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9498900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E45" s="3">
         <v>346700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>51400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>126200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>170100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>162400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>395600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>221800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15319300</v>
+      </c>
+      <c r="E46" s="3">
         <v>17171600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16001200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17848400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16130300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16529500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17133600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15399900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16535600</v>
+      </c>
+      <c r="E47" s="3">
         <v>16803700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16823100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17491900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17562900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16693900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14904600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13822400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35692800</v>
+      </c>
+      <c r="E48" s="3">
         <v>34578600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34047600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34028700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24214500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23597400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22612600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22249300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E49" s="3">
         <v>46100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>46700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>33800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>33600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>33500</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>659800</v>
+      </c>
+      <c r="E52" s="3">
         <v>95100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>155800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>98600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>170100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68392700</v>
+      </c>
+      <c r="E54" s="3">
         <v>69452200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>67945300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70572300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59469600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>58446300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56325800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52601300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,13 +2135,14 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>667400</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
@@ -2020,174 +2150,192 @@
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>531300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>580000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>499000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1111900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2449600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4326100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4646000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4127500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4029100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4371500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3199700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1651600</v>
+      </c>
+      <c r="E59" s="3">
         <v>2161100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1984500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2477400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1946600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2671800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2862100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2095500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5897800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7697800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7755800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8111000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7059700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7595900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7957000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6407200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17405500</v>
+      </c>
+      <c r="E61" s="3">
         <v>16372600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14603100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16027900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8543200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8185800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6893500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7215100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E62" s="3">
         <v>175600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>150300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>93000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2200</v>
       </c>
       <c r="H62" s="3">
         <v>2200</v>
       </c>
       <c r="I62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J62" s="3">
         <v>1700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24546300</v>
+      </c>
+      <c r="E66" s="3">
         <v>25403700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23679700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25408000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16624500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16671000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15720700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14469300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>35480300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35495100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35429500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35024200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34669400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33348700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30241100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41473700</v>
+      </c>
+      <c r="E76" s="3">
         <v>41800900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42059200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42963800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42253800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41192300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>39987200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37444900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>810600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1185500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1184900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1692200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1314500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2181800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3978500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3943100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>68500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>68700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>64400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>1851000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1427500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>87800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>912100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>865800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>488300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-102000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,8 +3142,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1557700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6417800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-125600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-490800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-937100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-935200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1115600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1117700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1117600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1124000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1045400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>909400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>771900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>-693400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2732400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6675100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1386600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-753500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-476500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1930000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-53100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>48500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-40700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-87100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>134000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>1149000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>199800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>352300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-551600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-419200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1012500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1026800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>177700</v>
+        <v>-262800</v>
       </c>
       <c r="E14" s="3">
         <v>6000</v>
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>26100</v>
+        <v>25000</v>
       </c>
       <c r="E15" s="3">
         <v>26000</v>
@@ -973,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2153300</v>
+        <v>2593800</v>
       </c>
       <c r="E17" s="3">
         <v>2712300</v>
@@ -1006,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1098200</v>
+        <v>657700</v>
       </c>
       <c r="E18" s="3">
         <v>817000</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1497300</v>
+        <v>1055700</v>
       </c>
       <c r="E21" s="3">
         <v>1528800</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>109600</v>
+        <v>116900</v>
       </c>
       <c r="E42" s="3">
         <v>77300</v>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>54800</v>
+        <v>47500</v>
       </c>
       <c r="E45" s="3">
         <v>346700</v>
@@ -1848,7 +1848,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>16535600</v>
+        <v>16584100</v>
       </c>
       <c r="E47" s="3">
         <v>16803700</v>
@@ -2013,7 +2013,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>659800</v>
+        <v>66200</v>
       </c>
       <c r="E52" s="3">
         <v>95100</v>
@@ -2141,8 +2141,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>667400</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1651600</v>
+        <v>2319000</v>
       </c>
       <c r="E59" s="3">
         <v>2161100</v>
@@ -2618,8 +2618,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>35381100</v>
       </c>
       <c r="E72" s="3">
         <v>35480300</v>
@@ -2902,8 +2902,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>62700</v>
       </c>
       <c r="E83" s="3">
         <v>68500</v>
@@ -3100,8 +3100,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>1969400</v>
       </c>
       <c r="E89" s="3">
         <v>1851000</v>
@@ -3247,8 +3247,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-240500</v>
       </c>
       <c r="E94" s="3">
         <v>2000</v>
@@ -3296,7 +3296,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1122000</v>
       </c>
       <c r="E96" s="3">
         <v>1115600</v>
@@ -3427,8 +3427,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-2729200</v>
       </c>
       <c r="E100" s="3">
         <v>-693400</v>
@@ -3460,8 +3460,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-10700</v>
       </c>
       <c r="E101" s="3">
         <v>-10600</v>
@@ -3494,7 +3494,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-1011000</v>
       </c>
       <c r="E102" s="3">
         <v>1149000</v>

--- a/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLDCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3307100</v>
+      </c>
+      <c r="E8" s="3">
         <v>3251500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3529300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3276900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3017200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3227000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3104800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2806900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3578400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2263900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2105700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2269900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1940300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1457900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1253800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1463200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1286800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1960600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1043200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1145800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1259400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1336600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1559300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1973200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1641700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1520200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1617900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-173800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-262800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-292900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>294800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-401500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1538700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1937800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2748000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2593800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2712300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2382200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1809000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1595300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1857000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1565500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2380100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>559100</v>
+      </c>
+      <c r="E18" s="3">
         <v>657700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>817000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>894700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1208200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1631700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1247900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1241400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1198300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-328800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-373000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-685900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-582400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-487300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-382900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-726400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1552400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1184100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1055700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1528800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1501300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1714600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2024600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1982600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2802500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2394500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>287500</v>
+      </c>
+      <c r="E22" s="3">
         <v>291100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>246800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>102600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>125600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>139700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>128900</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>831300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1060600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1336900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1382500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1972100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1639800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2450300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4277100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4272400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>122900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>163800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>258800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>313500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>261500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>271100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>283700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>837400</v>
+      </c>
+      <c r="E26" s="3">
         <v>937600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1251700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1218800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1713300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1326300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2188800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4006000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3988600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>726300</v>
+      </c>
+      <c r="E27" s="3">
         <v>810600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1185500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1184900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1692200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1314500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2181800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3978500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3943100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E32" s="3">
         <v>373000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>685900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>582400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>487300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>382900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>726400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1552400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1184100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>726300</v>
+      </c>
+      <c r="E33" s="3">
         <v>810600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1185500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1184900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1692200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1314500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2181800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3978500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3943100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>726300</v>
+      </c>
+      <c r="E35" s="3">
         <v>810600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1185500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1184900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1692200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1314500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2181800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3978500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3943100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,305 +1729,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2852000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2306900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2768000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1448600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1403900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>749000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1378100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2107800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3157800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E42" s="3">
         <v>116900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>77300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>64500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>49800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>42000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>870100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1146700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1293500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1124600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1440200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1522800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1885200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1915600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2222800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10229500</v>
+      </c>
+      <c r="E44" s="3">
         <v>11021300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12054000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12473300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14001500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13034300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12902000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12408700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9498900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E45" s="3">
         <v>47500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>346700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>126200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>170100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>162400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>395600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>221800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14773800</v>
+      </c>
+      <c r="E46" s="3">
         <v>15319300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17171600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16001200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17848400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16130300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16529500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17133600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15399900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17247800</v>
+      </c>
+      <c r="E47" s="3">
         <v>16584100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16803700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16823100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17491900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17562900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16693900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14904600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13822400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36379700</v>
+      </c>
+      <c r="E48" s="3">
         <v>35692800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34578600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34047600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34028700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24214500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23597400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22612600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22249300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E49" s="3">
         <v>45800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>46100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>46700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>33800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>33600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33500</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E52" s="3">
         <v>66200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>95100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>155800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>170100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>58200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>69298500</v>
+      </c>
+      <c r="E54" s="3">
         <v>68392700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69452200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67945300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>70572300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59469600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>58446300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56325800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52601300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,8 +2265,9 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2153,189 +2283,207 @@
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>531300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>580000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>499000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1111900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1603400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2449600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4326100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4646000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4127500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4029100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4000700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4371500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3199700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2086400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2319000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2161100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1984500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2477400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1946600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2671800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2862100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2095500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5897800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7697800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7755800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8111000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7059700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7595900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7957000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6407200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19563800</v>
+      </c>
+      <c r="E61" s="3">
         <v>17405500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16372600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14603100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16027900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8543200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8185800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6893500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7215100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E62" s="3">
         <v>130000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>175600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>150300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>93000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2200</v>
       </c>
       <c r="I62" s="3">
         <v>2200</v>
       </c>
       <c r="J62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25502200</v>
+      </c>
+      <c r="E66" s="3">
         <v>24546300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25403700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23679700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25408000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16624500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16671000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15720700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14469300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34933400</v>
+      </c>
+      <c r="E72" s="3">
         <v>35381100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35480300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35495100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35429500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35024200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>34669400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33348700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30241100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41429500</v>
+      </c>
+      <c r="E76" s="3">
         <v>41473700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41800900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42059200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42963800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>42253800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41192300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>39987200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37444900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>726300</v>
+      </c>
+      <c r="E81" s="3">
         <v>810600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1185500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1184900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1692200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1314500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2181800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3978500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3943100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E83" s="3">
         <v>62700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>68500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>55200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>48400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1583500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1969400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1851000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1427500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>87800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>912100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>865800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>488300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-102000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,8 +3362,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3175,9 +3395,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1076100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-240500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1557700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6417800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-125600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-490800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-937100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-935200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3522,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1119700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1122000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1115600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1117700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1117600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1124000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1045400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>909400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>771900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-610000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2729200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-693400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2732400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6675100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1386600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-753500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-476500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1930000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-53100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>48500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-40700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-87100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>134000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-93300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1011000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1149000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>199800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>352300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-551600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-419200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1012500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1026800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
